--- a/books.xlsx
+++ b/books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\OneDrive\github\book-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93420E7-0768-4F3E-91CE-324CFEA3252C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D445736B-70B6-4FE2-A072-EB2AA4171A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Название</t>
   </si>
@@ -83,66 +83,6 @@
   </si>
   <si>
     <t>Популярные тропы</t>
-  </si>
-  <si>
-    <t>Мара и Морок. Трилогия</t>
-  </si>
-  <si>
-    <t>t3UgEQAAQBAJ</t>
-  </si>
-  <si>
-    <t>Лия Арден</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Young Adult Fiction / General; Literary Collections / General</t>
-  </si>
-  <si>
-    <t>web_user</t>
-  </si>
-  <si>
-    <t>Вероника</t>
-  </si>
-  <si>
-    <t>крутота</t>
-  </si>
-  <si>
-    <t>от ненавести до любви_x000D_
-запретная любовь_x000D_
-апвап_x000D_
-исмчис</t>
-  </si>
-  <si>
-    <t>Мара и Морок. Графический роман. Том 1</t>
-  </si>
-  <si>
-    <t>OhJ2EQAAQBAJ</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>Невеста Ноября</t>
-  </si>
-  <si>
-    <t>IuNkEAAAQBAJ</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>Хороших девочек не убивают</t>
-  </si>
-  <si>
-    <t>fglWEAAAQBAJ</t>
-  </si>
-  <si>
-    <t>Холли Джексон</t>
-  </si>
-  <si>
-    <t>2021</t>
   </si>
 </sst>
 </file>
@@ -209,155 +149,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="571500" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="571500" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="571500" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="571500" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 4" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -638,155 +429,16 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>1082</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46082</v>
-      </c>
-      <c r="L2" s="2">
-        <v>46101</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>5</v>
-      </c>
-      <c r="P2">
-        <v>4</v>
-      </c>
-      <c r="Q2">
-        <v>5</v>
-      </c>
-      <c r="R2">
-        <v>3</v>
-      </c>
-      <c r="S2">
-        <v>3</v>
-      </c>
-      <c r="T2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3">
-        <v>114</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4">
-        <v>341</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5">
-        <v>402</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
+    <row r="3" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:21" ht="90" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>